--- a/design/templates/generated/North_Central/POULTRY_FLOOD_NCE_V1_upload_template.xlsx
+++ b/design/templates/generated/North_Central/POULTRY_FLOOD_NCE_V1_upload_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2021-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-2030" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEIGHTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_META" sheetId="5" state="hidden" r:id="rId5"/>
@@ -572,7 +572,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2020-2025 - Livestock Sector / Poultry Farming - Flood - North Central Province   [profile POULTRY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2021-2025 - Livestock Sector / Poultry Farming - Flood - North Central Province   [profile POULTRY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2025</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2020-2025</t>
+          <t>Dept. report 2021-2025</t>
         </is>
       </c>
       <c r="AF4" s="6" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NCE-001</t>
+          <t>AN1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2025</v>
@@ -1086,7 +1086,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NCE-002</t>
+          <t>AN2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2025</v>
@@ -1136,7 +1136,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NCE-003</t>
+          <t>AN3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2025</v>
@@ -1186,7 +1186,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NCE-004</t>
+          <t>AN4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2025</v>
@@ -1236,7 +1236,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NCE-005</t>
+          <t>AN5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2025</v>
@@ -1286,7 +1286,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NCE-006</t>
+          <t>AN6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2025</v>
@@ -1336,7 +1336,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NCE-007</t>
+          <t>AN7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2025</v>
@@ -1386,7 +1386,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NCE-008</t>
+          <t>AN8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2025</v>
@@ -1436,7 +1436,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NCE-009</t>
+          <t>AN9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2025</v>
@@ -1486,7 +1486,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NCE-010</t>
+          <t>AN10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2025</v>
@@ -1536,7 +1536,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NCE-011</t>
+          <t>AN11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2025</v>
@@ -1586,7 +1586,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NCE-012</t>
+          <t>AN12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2025</v>
@@ -1636,7 +1636,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NCE-013</t>
+          <t>AN13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2025</v>
@@ -1686,7 +1686,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NCE-014</t>
+          <t>AN14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2025</v>
@@ -1736,7 +1736,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NCE-015</t>
+          <t>AN15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2025</v>
@@ -1786,7 +1786,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NCE-016</t>
+          <t>AN16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2025</v>
@@ -1836,7 +1836,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NCE-017</t>
+          <t>AN17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2025</v>
@@ -1886,7 +1886,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NCE-018</t>
+          <t>AN18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2025</v>
@@ -1936,7 +1936,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NCE-019</t>
+          <t>AN19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2025</v>
@@ -1986,7 +1986,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NCE-020</t>
+          <t>AN20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2025</v>
@@ -2036,7 +2036,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NCE-021</t>
+          <t>AN21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2025</v>
@@ -2086,7 +2086,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NCE-022</t>
+          <t>AN22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2025</v>
@@ -2136,7 +2136,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NCE-023</t>
+          <t>PO1</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2025</v>
@@ -2186,7 +2186,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NCE-024</t>
+          <t>PO2</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2025</v>
@@ -2236,7 +2236,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NCE-025</t>
+          <t>PO3</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2025</v>
@@ -2286,7 +2286,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NCE-026</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2025</v>
@@ -2336,7 +2336,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NCE-027</t>
+          <t>PO5</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2025</v>
@@ -2386,7 +2386,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NCE-028</t>
+          <t>PO6</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2025</v>
@@ -2436,7 +2436,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NCE-029</t>
+          <t>PO7</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2025</v>
@@ -2484,7 +2484,6 @@
       <c r="AF33" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AF1"/>
   </mergeCells>
@@ -2543,7 +2542,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2025-2030 - Livestock Sector / Poultry Farming - Flood - North Central Province   [profile POULTRY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2026-2030 - Livestock Sector / Poultry Farming - Flood - North Central Province   [profile POULTRY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2912,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2030</v>
@@ -2995,7 +2994,7 @@
       </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2025-2030</t>
+          <t>Dept. report 2026-2030</t>
         </is>
       </c>
       <c r="AF4" s="6" t="inlineStr">
@@ -3007,7 +3006,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NCE-001</t>
+          <t>AN1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3021,7 +3020,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2030</v>
@@ -3057,7 +3056,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NCE-002</t>
+          <t>AN2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3071,7 +3070,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2030</v>
@@ -3107,7 +3106,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NCE-003</t>
+          <t>AN3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3121,7 +3120,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2030</v>
@@ -3157,7 +3156,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NCE-004</t>
+          <t>AN4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3171,7 +3170,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2030</v>
@@ -3207,7 +3206,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NCE-005</t>
+          <t>AN5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -3221,7 +3220,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2030</v>
@@ -3257,7 +3256,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NCE-006</t>
+          <t>AN6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3271,7 +3270,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2030</v>
@@ -3307,7 +3306,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NCE-007</t>
+          <t>AN7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -3321,7 +3320,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2030</v>
@@ -3357,7 +3356,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NCE-008</t>
+          <t>AN8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3371,7 +3370,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2030</v>
@@ -3407,7 +3406,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NCE-009</t>
+          <t>AN9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -3421,7 +3420,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2030</v>
@@ -3457,7 +3456,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NCE-010</t>
+          <t>AN10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -3471,7 +3470,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2030</v>
@@ -3507,7 +3506,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NCE-011</t>
+          <t>AN11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -3521,7 +3520,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2030</v>
@@ -3557,7 +3556,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NCE-012</t>
+          <t>AN12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3571,7 +3570,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2030</v>
@@ -3607,7 +3606,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NCE-013</t>
+          <t>AN13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3621,7 +3620,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2030</v>
@@ -3657,7 +3656,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NCE-014</t>
+          <t>AN14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -3671,7 +3670,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2030</v>
@@ -3707,7 +3706,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NCE-015</t>
+          <t>AN15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -3721,7 +3720,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2030</v>
@@ -3757,7 +3756,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NCE-016</t>
+          <t>AN16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -3771,7 +3770,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2030</v>
@@ -3807,7 +3806,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NCE-017</t>
+          <t>AN17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -3821,7 +3820,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2030</v>
@@ -3857,7 +3856,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NCE-018</t>
+          <t>AN18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -3871,7 +3870,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2030</v>
@@ -3907,7 +3906,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NCE-019</t>
+          <t>AN19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -3921,7 +3920,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2030</v>
@@ -3957,7 +3956,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NCE-020</t>
+          <t>AN20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -3971,7 +3970,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2030</v>
@@ -4007,7 +4006,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NCE-021</t>
+          <t>AN21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -4021,7 +4020,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2030</v>
@@ -4057,7 +4056,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NCE-022</t>
+          <t>AN22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -4071,7 +4070,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2030</v>
@@ -4107,7 +4106,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NCE-023</t>
+          <t>PO1</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -4121,7 +4120,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2030</v>
@@ -4157,7 +4156,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NCE-024</t>
+          <t>PO2</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -4171,7 +4170,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2030</v>
@@ -4207,7 +4206,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NCE-025</t>
+          <t>PO3</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -4221,7 +4220,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2030</v>
@@ -4257,7 +4256,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NCE-026</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -4271,7 +4270,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2030</v>
@@ -4307,7 +4306,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NCE-027</t>
+          <t>PO5</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -4321,7 +4320,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2030</v>
@@ -4357,7 +4356,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NCE-028</t>
+          <t>PO6</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -4371,7 +4370,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2030</v>
@@ -4407,7 +4406,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NCE-029</t>
+          <t>PO7</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -4421,7 +4420,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2030</v>
@@ -4455,7 +4454,6 @@
       <c r="AF33" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AF1"/>
   </mergeCells>
@@ -4474,7 +4472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4483,6 +4481,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4530,6 +4529,11 @@
           <t>PROPOSED WEIGHT % (read at import)</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>basis of the proposal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4550,6 +4554,7 @@
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="12" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -4578,6 +4583,7 @@
       <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="G5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -4598,6 +4604,7 @@
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="12" t="n"/>
+      <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -4618,6 +4625,7 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
+      <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4638,6 +4646,7 @@
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
+      <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -4658,6 +4667,7 @@
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
+      <c r="G9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -4678,6 +4688,7 @@
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
+      <c r="G10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -4698,6 +4709,7 @@
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
+      <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -4718,6 +4730,7 @@
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
+      <c r="G12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -4746,6 +4759,7 @@
       <c r="F13" s="12" t="n">
         <v>25</v>
       </c>
+      <c r="G13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -4766,6 +4780,7 @@
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
+      <c r="G14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -4786,6 +4801,7 @@
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
+      <c r="G15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -4806,6 +4822,7 @@
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
+      <c r="G16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -4826,6 +4843,7 @@
       <c r="D17" s="11" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
+      <c r="G17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -4846,6 +4864,7 @@
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
+      <c r="G18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -4866,6 +4885,7 @@
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
+      <c r="G19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -4886,6 +4906,7 @@
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
+      <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -4914,6 +4935,7 @@
       <c r="F21" s="12" t="n">
         <v>25</v>
       </c>
+      <c r="G21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -4934,6 +4956,7 @@
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="12" t="n"/>
+      <c r="G22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -4962,6 +4985,7 @@
       <c r="F23" s="12" t="n">
         <v>25</v>
       </c>
+      <c r="G23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -4982,6 +5006,7 @@
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="12" t="n"/>
+      <c r="G24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -5002,6 +5027,7 @@
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="12" t="n"/>
+      <c r="G25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -5030,6 +5056,7 @@
       <c r="F26" s="12" t="n">
         <v>25</v>
       </c>
+      <c r="G26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -5050,6 +5077,7 @@
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="12" t="n"/>
+      <c r="G27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -5070,6 +5098,7 @@
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="12" t="n"/>
+      <c r="G28" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -5094,9 +5123,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
@@ -5135,14 +5163,14 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: POULTRY_FLOOD_NCE_V1   |   generated 2026-07-29 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: POULTRY_FLOOD_NCE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. One tab per data period (2020-2025, 2025-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
+          <t>1. One tab per data period (2021-2025, 2026-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
         </is>
       </c>
     </row>
@@ -5156,14 +5184,14 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2b. The year 2025 appears in both tabs. If a year sits in two periods the system uses the LATER period's value, so nothing is counted twice.</t>
+          <t>2b. The two periods are contiguous and do not overlap (changed 2026-09-03 at the Central panel's request - the old 2020-2025 / 2025-2030 pair shared the year 2025 and needed a tie-break). Every year belongs to exactly one tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>3. Edit ONLY the yellow cells. Division codes, names, district and the period columns are pre-filled and locked.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5205,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Do not add, remove, rename or reorder columns or tabs. Files with changed structure are rejected on import.</t>
+          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5977,80 +6005,104 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>generated</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>unlocked-review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dsd_level</t>
+          <t>panel_overrides</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>DS_DIVISION</t>
+          <t>0 add, 0 retire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>periods</t>
+          <t>generated</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2020-2025|2025-2030</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>n_variables</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>25</v>
+          <t>dsd_level</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>DS_DIVISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>period_rule_default</t>
+          <t>periods</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>average (typical year); 2025 -&gt; latest period wins</t>
+          <t>2021-2025|2026-2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>period_aggregation</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|ANNUAL_EGG_PRODUCTION=average|BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY=average|BACKYARD_POULTRY_FARMS=average|BROILER_FARMS=average|DAILY_EGG_PRODUCTION=average|EGG_COLLECTORS=average|EGG_LAYING_HENS=average|FARM_SHOP=average|LAYER_FARMS=average|LIVE_BIRD_COLLECTORS=average|MEAT_PROCESSING_PLANTS=average|MONTHLY_EGG_PRODUCTION=average|PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS=average|PCT_POULTRY_RAISING_FAMERS=average|POULTRY_FARMERS=average|POULTRY_FEED_MANUFACTURES_COMMERCIAL=average|POULTRY_FEED_SELF_MIXED_MIXERS=average|POULTRY_POPULATION=average|SLAUGHTER_HOUSES_MUNICIPAL=average|SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS=average</t>
-        </is>
+          <t>n_variables</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>period_rule_default</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>average (typical year); periods are contiguous, no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>period_aggregation</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|ANNUAL_EGG_PRODUCTION=average|BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY=average|BACKYARD_POULTRY_FARMS=average|BROILER_FARMS=average|DAILY_EGG_PRODUCTION=average|EGG_COLLECTORS=average|EGG_LAYING_HENS=average|FARM_SHOP=average|LAYER_FARMS=average|LIVE_BIRD_COLLECTORS=average|MEAT_PROCESSING_PLANTS=average|MONTHLY_EGG_PRODUCTION=average|PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS=average|PCT_POULTRY_RAISING_FAMERS=average|POULTRY_FARMERS=average|POULTRY_FEED_MANUFACTURES_COMMERCIAL=average|POULTRY_FEED_SELF_MIXED_MIXERS=average|POULTRY_POPULATION=average|SLAUGHTER_HOUSES_MUNICIPAL=average|SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS=average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>expected_columns</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|VERY_WET_DAYS|ANNUAL_EGG_PRODUCTION|BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY|BACKYARD_POULTRY_FARMS|BROILER_FARMS|DAILY_EGG_PRODUCTION|EGG_COLLECTORS|EGG_LAYING_HENS|FARM_SHOP|LAYER_FARMS|LIVE_BIRD_COLLECTORS|MEAT_PROCESSING_PLANTS|MONTHLY_EGG_PRODUCTION|PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS|PCT_POULTRY_RAISING_FAMERS|POULTRY_FARMERS|POULTRY_FEED_MANUFACTURES_COMMERCIAL|POULTRY_FEED_SELF_MIXED_MIXERS|POULTRY_POPULATION|SLAUGHTER_HOUSES_MUNICIPAL|SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS|DATA_SOURCE|NOTES</t>
         </is>

--- a/design/templates/generated/North_Central/POULTRY_FLOOD_NCE_V1_upload_template.xlsx
+++ b/design/templates/generated/North_Central/POULTRY_FLOOD_NCE_V1_upload_template.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF33"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -567,6 +567,10 @@
     <col width="16" customWidth="1" min="30" max="30"/>
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -604,135 +608,155 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>FLOOD_EVENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>FLOOD_HAZARD_INDEX</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>VERY_WET_DAYS</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>ANNUAL_EGG_PRODUCTION</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>BACKYARD_POULTRY_FARMS</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>BROILER_FARMS</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>DAILY_EGG_PRODUCTION</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>EGG_COLLECTORS</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>EGG_LAYING_HENS</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>FARM_SHOP</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>LAYER_FARMS</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>LIVE_BIRD_COLLECTORS</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>MEAT_PROCESSING_PLANTS</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>MONTHLY_EGG_PRODUCTION</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>PCT_POULTRY_RAISING_FAMERS</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_FARMERS</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AD2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_FEED_MANUFACTURES_COMMERCIAL</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_FEED_SELF_MIXED_MIXERS</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_POPULATION</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>SLAUGHTER_HOUSES_MUNICIPAL</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>DATA_SOURCE</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -766,160 +790,184 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>hazard: No. of Flood events_ 1974-2004_25%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>hazard: No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: No. of Flood events_ 2005-2023_75%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>hazard: Flood Hazard Index
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>hazard: No. of lightning incidents  - 1974 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>hazard: Strong wind events - 1978 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: 3 day cumulative rain fall
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>hazard: Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: Very wet days (95th percentile)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>exposure: Egg Production (Annual)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Backyard hatcheries -DOC production / weekly
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Backyard Poultry Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Broiler Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>exposure: Daily Egg Production
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of egg collectors
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Egg Laying Hens
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of farm shop
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Layer Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>exposure: No.of live bird collectors
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of meat processing plants
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>exposure: Monthly Egg Production
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Poultry Farmers from total livestock farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>exposure: % of Poultry raising famers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>exposure: # Poultry Farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of poultry feed manufactures(commercial)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of poultry feed (self mixed) mixers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AB3" s="5" t="inlineStr">
+      <c r="AF3" s="5" t="inlineStr">
         <is>
           <t>exposure: Poultry Population
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AG3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of slaughter houses ( municipal )
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AH3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of small scale poultry processing establishments ( manual processors)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AE3" s="5" t="inlineStr">
+      <c r="AI3" s="5" t="inlineStr">
         <is>
           <t>origin of the numbers</t>
         </is>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
+      <c r="AJ3" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
@@ -1022,12 +1070,24 @@
       <c r="AD4" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="AE4" s="6" t="inlineStr">
+      <c r="AE4" s="6" t="n">
+        <v>1037.5</v>
+      </c>
+      <c r="AF4" s="6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="AG4" s="6" t="n">
+        <v>1112.5</v>
+      </c>
+      <c r="AH4" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AI4" s="6" t="inlineStr">
         <is>
           <t>Dept. report 2021-2025</t>
         </is>
       </c>
-      <c r="AF4" s="6" t="inlineStr">
+      <c r="AJ4" s="6" t="inlineStr">
         <is>
           <t>example row</t>
         </is>
@@ -1082,6 +1142,10 @@
       <c r="AD5" s="8" t="n"/>
       <c r="AE5" s="8" t="n"/>
       <c r="AF5" s="8" t="n"/>
+      <c r="AG5" s="8" t="n"/>
+      <c r="AH5" s="8" t="n"/>
+      <c r="AI5" s="8" t="n"/>
+      <c r="AJ5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1132,6 +1196,10 @@
       <c r="AD6" s="8" t="n"/>
       <c r="AE6" s="8" t="n"/>
       <c r="AF6" s="8" t="n"/>
+      <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1182,6 +1250,10 @@
       <c r="AD7" s="8" t="n"/>
       <c r="AE7" s="8" t="n"/>
       <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8" t="n"/>
+      <c r="AI7" s="8" t="n"/>
+      <c r="AJ7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1232,6 +1304,10 @@
       <c r="AD8" s="8" t="n"/>
       <c r="AE8" s="8" t="n"/>
       <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8" t="n"/>
+      <c r="AI8" s="8" t="n"/>
+      <c r="AJ8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1282,6 +1358,10 @@
       <c r="AD9" s="8" t="n"/>
       <c r="AE9" s="8" t="n"/>
       <c r="AF9" s="8" t="n"/>
+      <c r="AG9" s="8" t="n"/>
+      <c r="AH9" s="8" t="n"/>
+      <c r="AI9" s="8" t="n"/>
+      <c r="AJ9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1332,6 +1412,10 @@
       <c r="AD10" s="8" t="n"/>
       <c r="AE10" s="8" t="n"/>
       <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8" t="n"/>
+      <c r="AI10" s="8" t="n"/>
+      <c r="AJ10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1382,6 +1466,10 @@
       <c r="AD11" s="8" t="n"/>
       <c r="AE11" s="8" t="n"/>
       <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8" t="n"/>
+      <c r="AI11" s="8" t="n"/>
+      <c r="AJ11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1432,6 +1520,10 @@
       <c r="AD12" s="8" t="n"/>
       <c r="AE12" s="8" t="n"/>
       <c r="AF12" s="8" t="n"/>
+      <c r="AG12" s="8" t="n"/>
+      <c r="AH12" s="8" t="n"/>
+      <c r="AI12" s="8" t="n"/>
+      <c r="AJ12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1482,6 +1574,10 @@
       <c r="AD13" s="8" t="n"/>
       <c r="AE13" s="8" t="n"/>
       <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8" t="n"/>
+      <c r="AI13" s="8" t="n"/>
+      <c r="AJ13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1532,6 +1628,10 @@
       <c r="AD14" s="8" t="n"/>
       <c r="AE14" s="8" t="n"/>
       <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8" t="n"/>
+      <c r="AI14" s="8" t="n"/>
+      <c r="AJ14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1582,6 +1682,10 @@
       <c r="AD15" s="8" t="n"/>
       <c r="AE15" s="8" t="n"/>
       <c r="AF15" s="8" t="n"/>
+      <c r="AG15" s="8" t="n"/>
+      <c r="AH15" s="8" t="n"/>
+      <c r="AI15" s="8" t="n"/>
+      <c r="AJ15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1632,6 +1736,10 @@
       <c r="AD16" s="8" t="n"/>
       <c r="AE16" s="8" t="n"/>
       <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8" t="n"/>
+      <c r="AI16" s="8" t="n"/>
+      <c r="AJ16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1682,6 +1790,10 @@
       <c r="AD17" s="8" t="n"/>
       <c r="AE17" s="8" t="n"/>
       <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8" t="n"/>
+      <c r="AI17" s="8" t="n"/>
+      <c r="AJ17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1732,6 +1844,10 @@
       <c r="AD18" s="8" t="n"/>
       <c r="AE18" s="8" t="n"/>
       <c r="AF18" s="8" t="n"/>
+      <c r="AG18" s="8" t="n"/>
+      <c r="AH18" s="8" t="n"/>
+      <c r="AI18" s="8" t="n"/>
+      <c r="AJ18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1782,6 +1898,10 @@
       <c r="AD19" s="8" t="n"/>
       <c r="AE19" s="8" t="n"/>
       <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8" t="n"/>
+      <c r="AI19" s="8" t="n"/>
+      <c r="AJ19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1832,6 +1952,10 @@
       <c r="AD20" s="8" t="n"/>
       <c r="AE20" s="8" t="n"/>
       <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8" t="n"/>
+      <c r="AI20" s="8" t="n"/>
+      <c r="AJ20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1882,6 +2006,10 @@
       <c r="AD21" s="8" t="n"/>
       <c r="AE21" s="8" t="n"/>
       <c r="AF21" s="8" t="n"/>
+      <c r="AG21" s="8" t="n"/>
+      <c r="AH21" s="8" t="n"/>
+      <c r="AI21" s="8" t="n"/>
+      <c r="AJ21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1932,6 +2060,10 @@
       <c r="AD22" s="8" t="n"/>
       <c r="AE22" s="8" t="n"/>
       <c r="AF22" s="8" t="n"/>
+      <c r="AG22" s="8" t="n"/>
+      <c r="AH22" s="8" t="n"/>
+      <c r="AI22" s="8" t="n"/>
+      <c r="AJ22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1982,6 +2114,10 @@
       <c r="AD23" s="8" t="n"/>
       <c r="AE23" s="8" t="n"/>
       <c r="AF23" s="8" t="n"/>
+      <c r="AG23" s="8" t="n"/>
+      <c r="AH23" s="8" t="n"/>
+      <c r="AI23" s="8" t="n"/>
+      <c r="AJ23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -2032,6 +2168,10 @@
       <c r="AD24" s="8" t="n"/>
       <c r="AE24" s="8" t="n"/>
       <c r="AF24" s="8" t="n"/>
+      <c r="AG24" s="8" t="n"/>
+      <c r="AH24" s="8" t="n"/>
+      <c r="AI24" s="8" t="n"/>
+      <c r="AJ24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2082,6 +2222,10 @@
       <c r="AD25" s="8" t="n"/>
       <c r="AE25" s="8" t="n"/>
       <c r="AF25" s="8" t="n"/>
+      <c r="AG25" s="8" t="n"/>
+      <c r="AH25" s="8" t="n"/>
+      <c r="AI25" s="8" t="n"/>
+      <c r="AJ25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -2132,6 +2276,10 @@
       <c r="AD26" s="8" t="n"/>
       <c r="AE26" s="8" t="n"/>
       <c r="AF26" s="8" t="n"/>
+      <c r="AG26" s="8" t="n"/>
+      <c r="AH26" s="8" t="n"/>
+      <c r="AI26" s="8" t="n"/>
+      <c r="AJ26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -2182,6 +2330,10 @@
       <c r="AD27" s="8" t="n"/>
       <c r="AE27" s="8" t="n"/>
       <c r="AF27" s="8" t="n"/>
+      <c r="AG27" s="8" t="n"/>
+      <c r="AH27" s="8" t="n"/>
+      <c r="AI27" s="8" t="n"/>
+      <c r="AJ27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -2232,6 +2384,10 @@
       <c r="AD28" s="8" t="n"/>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
+      <c r="AG28" s="8" t="n"/>
+      <c r="AH28" s="8" t="n"/>
+      <c r="AI28" s="8" t="n"/>
+      <c r="AJ28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2282,6 +2438,10 @@
       <c r="AD29" s="8" t="n"/>
       <c r="AE29" s="8" t="n"/>
       <c r="AF29" s="8" t="n"/>
+      <c r="AG29" s="8" t="n"/>
+      <c r="AH29" s="8" t="n"/>
+      <c r="AI29" s="8" t="n"/>
+      <c r="AJ29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -2332,6 +2492,10 @@
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
       <c r="AF30" s="8" t="n"/>
+      <c r="AG30" s="8" t="n"/>
+      <c r="AH30" s="8" t="n"/>
+      <c r="AI30" s="8" t="n"/>
+      <c r="AJ30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -2382,6 +2546,10 @@
       <c r="AD31" s="8" t="n"/>
       <c r="AE31" s="8" t="n"/>
       <c r="AF31" s="8" t="n"/>
+      <c r="AG31" s="8" t="n"/>
+      <c r="AH31" s="8" t="n"/>
+      <c r="AI31" s="8" t="n"/>
+      <c r="AJ31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -2432,6 +2600,10 @@
       <c r="AD32" s="8" t="n"/>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
+      <c r="AG32" s="8" t="n"/>
+      <c r="AH32" s="8" t="n"/>
+      <c r="AI32" s="8" t="n"/>
+      <c r="AJ32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -2482,13 +2654,17 @@
       <c r="AD33" s="8" t="n"/>
       <c r="AE33" s="8" t="n"/>
       <c r="AF33" s="8" t="n"/>
+      <c r="AG33" s="8" t="n"/>
+      <c r="AH33" s="8" t="n"/>
+      <c r="AI33" s="8" t="n"/>
+      <c r="AJ33" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A1:AJ1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30 AB31 AB32 AB33 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30 AB31 AB32 AB33 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33 AE5 AE6 AE7 AE8 AE9 AE10 AE11 AE12 AE13 AE14 AE15 AE16 AE17 AE18 AE19 AE20 AE21 AE22 AE23 AE24 AE25 AE26 AE27 AE28 AE29 AE30 AE31 AE32 AE33 AF5 AF6 AF7 AF8 AF9 AF10 AF11 AF12 AF13 AF14 AF15 AF16 AF17 AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25 AF26 AF27 AF28 AF29 AF30 AF31 AF32 AF33 AG5 AG6 AG7 AG8 AG9 AG10 AG11 AG12 AG13 AG14 AG15 AG16 AG17 AG18 AG19 AG20 AG21 AG22 AG23 AG24 AG25 AG26 AG27 AG28 AG29 AG30 AG31 AG32 AG33 AH5 AH6 AH7 AH8 AH9 AH10 AH11 AH12 AH13 AH14 AH15 AH16 AH17 AH18 AH19 AH20 AH21 AH22 AH23 AH24 AH25 AH26 AH27 AH28 AH29 AH30 AH31 AH32 AH33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -2502,7 +2678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF33"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2537,6 +2713,10 @@
     <col width="16" customWidth="1" min="30" max="30"/>
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2574,135 +2754,155 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>FLOOD_EVENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>FLOOD_HAZARD_INDEX</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>VERY_WET_DAYS</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>ANNUAL_EGG_PRODUCTION</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>BACKYARD_POULTRY_FARMS</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>BROILER_FARMS</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>DAILY_EGG_PRODUCTION</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>EGG_COLLECTORS</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>EGG_LAYING_HENS</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>FARM_SHOP</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>LAYER_FARMS</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>LIVE_BIRD_COLLECTORS</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>MEAT_PROCESSING_PLANTS</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>MONTHLY_EGG_PRODUCTION</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>PCT_POULTRY_RAISING_FAMERS</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_FARMERS</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AD2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_FEED_MANUFACTURES_COMMERCIAL</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_FEED_SELF_MIXED_MIXERS</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>POULTRY_POPULATION</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>SLAUGHTER_HOUSES_MUNICIPAL</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>DATA_SOURCE</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -2736,160 +2936,184 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>hazard: No. of Flood events_ 1974-2004_25%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>hazard: No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: No. of Flood events_ 2005-2023_75%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>hazard: Flood Hazard Index
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>hazard: No. of lightning incidents  - 1974 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>hazard: Strong wind events - 1978 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: 3 day cumulative rain fall
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>hazard: Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: Very wet days (95th percentile)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>exposure: Egg Production (Annual)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Backyard hatcheries -DOC production / weekly
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Backyard Poultry Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Broiler Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>exposure: Daily Egg Production
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of egg collectors
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Egg Laying Hens
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of farm shop
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Layer Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>exposure: No.of live bird collectors
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of meat processing plants
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>exposure: Monthly Egg Production
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Poultry Farmers from total livestock farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>exposure: % of Poultry raising famers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>exposure: # Poultry Farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of poultry feed manufactures(commercial)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of poultry feed (self mixed) mixers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AB3" s="5" t="inlineStr">
+      <c r="AF3" s="5" t="inlineStr">
         <is>
           <t>exposure: Poultry Population
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AG3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of slaughter houses ( municipal )
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AH3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of small scale poultry processing establishments ( manual processors)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="AE3" s="5" t="inlineStr">
+      <c r="AI3" s="5" t="inlineStr">
         <is>
           <t>origin of the numbers</t>
         </is>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
+      <c r="AJ3" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
@@ -2992,12 +3216,24 @@
       <c r="AD4" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="AE4" s="6" t="inlineStr">
+      <c r="AE4" s="6" t="n">
+        <v>1037.5</v>
+      </c>
+      <c r="AF4" s="6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="AG4" s="6" t="n">
+        <v>1112.5</v>
+      </c>
+      <c r="AH4" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AI4" s="6" t="inlineStr">
         <is>
           <t>Dept. report 2026-2030</t>
         </is>
       </c>
-      <c r="AF4" s="6" t="inlineStr">
+      <c r="AJ4" s="6" t="inlineStr">
         <is>
           <t>example row</t>
         </is>
@@ -3052,6 +3288,10 @@
       <c r="AD5" s="8" t="n"/>
       <c r="AE5" s="8" t="n"/>
       <c r="AF5" s="8" t="n"/>
+      <c r="AG5" s="8" t="n"/>
+      <c r="AH5" s="8" t="n"/>
+      <c r="AI5" s="8" t="n"/>
+      <c r="AJ5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3102,6 +3342,10 @@
       <c r="AD6" s="8" t="n"/>
       <c r="AE6" s="8" t="n"/>
       <c r="AF6" s="8" t="n"/>
+      <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3152,6 +3396,10 @@
       <c r="AD7" s="8" t="n"/>
       <c r="AE7" s="8" t="n"/>
       <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8" t="n"/>
+      <c r="AI7" s="8" t="n"/>
+      <c r="AJ7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3202,6 +3450,10 @@
       <c r="AD8" s="8" t="n"/>
       <c r="AE8" s="8" t="n"/>
       <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8" t="n"/>
+      <c r="AI8" s="8" t="n"/>
+      <c r="AJ8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -3252,6 +3504,10 @@
       <c r="AD9" s="8" t="n"/>
       <c r="AE9" s="8" t="n"/>
       <c r="AF9" s="8" t="n"/>
+      <c r="AG9" s="8" t="n"/>
+      <c r="AH9" s="8" t="n"/>
+      <c r="AI9" s="8" t="n"/>
+      <c r="AJ9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -3302,6 +3558,10 @@
       <c r="AD10" s="8" t="n"/>
       <c r="AE10" s="8" t="n"/>
       <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8" t="n"/>
+      <c r="AI10" s="8" t="n"/>
+      <c r="AJ10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -3352,6 +3612,10 @@
       <c r="AD11" s="8" t="n"/>
       <c r="AE11" s="8" t="n"/>
       <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8" t="n"/>
+      <c r="AI11" s="8" t="n"/>
+      <c r="AJ11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3402,6 +3666,10 @@
       <c r="AD12" s="8" t="n"/>
       <c r="AE12" s="8" t="n"/>
       <c r="AF12" s="8" t="n"/>
+      <c r="AG12" s="8" t="n"/>
+      <c r="AH12" s="8" t="n"/>
+      <c r="AI12" s="8" t="n"/>
+      <c r="AJ12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -3452,6 +3720,10 @@
       <c r="AD13" s="8" t="n"/>
       <c r="AE13" s="8" t="n"/>
       <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8" t="n"/>
+      <c r="AI13" s="8" t="n"/>
+      <c r="AJ13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3502,6 +3774,10 @@
       <c r="AD14" s="8" t="n"/>
       <c r="AE14" s="8" t="n"/>
       <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8" t="n"/>
+      <c r="AI14" s="8" t="n"/>
+      <c r="AJ14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -3552,6 +3828,10 @@
       <c r="AD15" s="8" t="n"/>
       <c r="AE15" s="8" t="n"/>
       <c r="AF15" s="8" t="n"/>
+      <c r="AG15" s="8" t="n"/>
+      <c r="AH15" s="8" t="n"/>
+      <c r="AI15" s="8" t="n"/>
+      <c r="AJ15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -3602,6 +3882,10 @@
       <c r="AD16" s="8" t="n"/>
       <c r="AE16" s="8" t="n"/>
       <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8" t="n"/>
+      <c r="AI16" s="8" t="n"/>
+      <c r="AJ16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -3652,6 +3936,10 @@
       <c r="AD17" s="8" t="n"/>
       <c r="AE17" s="8" t="n"/>
       <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8" t="n"/>
+      <c r="AI17" s="8" t="n"/>
+      <c r="AJ17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -3702,6 +3990,10 @@
       <c r="AD18" s="8" t="n"/>
       <c r="AE18" s="8" t="n"/>
       <c r="AF18" s="8" t="n"/>
+      <c r="AG18" s="8" t="n"/>
+      <c r="AH18" s="8" t="n"/>
+      <c r="AI18" s="8" t="n"/>
+      <c r="AJ18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -3752,6 +4044,10 @@
       <c r="AD19" s="8" t="n"/>
       <c r="AE19" s="8" t="n"/>
       <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8" t="n"/>
+      <c r="AI19" s="8" t="n"/>
+      <c r="AJ19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -3802,6 +4098,10 @@
       <c r="AD20" s="8" t="n"/>
       <c r="AE20" s="8" t="n"/>
       <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8" t="n"/>
+      <c r="AI20" s="8" t="n"/>
+      <c r="AJ20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -3852,6 +4152,10 @@
       <c r="AD21" s="8" t="n"/>
       <c r="AE21" s="8" t="n"/>
       <c r="AF21" s="8" t="n"/>
+      <c r="AG21" s="8" t="n"/>
+      <c r="AH21" s="8" t="n"/>
+      <c r="AI21" s="8" t="n"/>
+      <c r="AJ21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3902,6 +4206,10 @@
       <c r="AD22" s="8" t="n"/>
       <c r="AE22" s="8" t="n"/>
       <c r="AF22" s="8" t="n"/>
+      <c r="AG22" s="8" t="n"/>
+      <c r="AH22" s="8" t="n"/>
+      <c r="AI22" s="8" t="n"/>
+      <c r="AJ22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -3952,6 +4260,10 @@
       <c r="AD23" s="8" t="n"/>
       <c r="AE23" s="8" t="n"/>
       <c r="AF23" s="8" t="n"/>
+      <c r="AG23" s="8" t="n"/>
+      <c r="AH23" s="8" t="n"/>
+      <c r="AI23" s="8" t="n"/>
+      <c r="AJ23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -4002,6 +4314,10 @@
       <c r="AD24" s="8" t="n"/>
       <c r="AE24" s="8" t="n"/>
       <c r="AF24" s="8" t="n"/>
+      <c r="AG24" s="8" t="n"/>
+      <c r="AH24" s="8" t="n"/>
+      <c r="AI24" s="8" t="n"/>
+      <c r="AJ24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -4052,6 +4368,10 @@
       <c r="AD25" s="8" t="n"/>
       <c r="AE25" s="8" t="n"/>
       <c r="AF25" s="8" t="n"/>
+      <c r="AG25" s="8" t="n"/>
+      <c r="AH25" s="8" t="n"/>
+      <c r="AI25" s="8" t="n"/>
+      <c r="AJ25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -4102,6 +4422,10 @@
       <c r="AD26" s="8" t="n"/>
       <c r="AE26" s="8" t="n"/>
       <c r="AF26" s="8" t="n"/>
+      <c r="AG26" s="8" t="n"/>
+      <c r="AH26" s="8" t="n"/>
+      <c r="AI26" s="8" t="n"/>
+      <c r="AJ26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -4152,6 +4476,10 @@
       <c r="AD27" s="8" t="n"/>
       <c r="AE27" s="8" t="n"/>
       <c r="AF27" s="8" t="n"/>
+      <c r="AG27" s="8" t="n"/>
+      <c r="AH27" s="8" t="n"/>
+      <c r="AI27" s="8" t="n"/>
+      <c r="AJ27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -4202,6 +4530,10 @@
       <c r="AD28" s="8" t="n"/>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
+      <c r="AG28" s="8" t="n"/>
+      <c r="AH28" s="8" t="n"/>
+      <c r="AI28" s="8" t="n"/>
+      <c r="AJ28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -4252,6 +4584,10 @@
       <c r="AD29" s="8" t="n"/>
       <c r="AE29" s="8" t="n"/>
       <c r="AF29" s="8" t="n"/>
+      <c r="AG29" s="8" t="n"/>
+      <c r="AH29" s="8" t="n"/>
+      <c r="AI29" s="8" t="n"/>
+      <c r="AJ29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -4302,6 +4638,10 @@
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
       <c r="AF30" s="8" t="n"/>
+      <c r="AG30" s="8" t="n"/>
+      <c r="AH30" s="8" t="n"/>
+      <c r="AI30" s="8" t="n"/>
+      <c r="AJ30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -4352,6 +4692,10 @@
       <c r="AD31" s="8" t="n"/>
       <c r="AE31" s="8" t="n"/>
       <c r="AF31" s="8" t="n"/>
+      <c r="AG31" s="8" t="n"/>
+      <c r="AH31" s="8" t="n"/>
+      <c r="AI31" s="8" t="n"/>
+      <c r="AJ31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -4402,6 +4746,10 @@
       <c r="AD32" s="8" t="n"/>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
+      <c r="AG32" s="8" t="n"/>
+      <c r="AH32" s="8" t="n"/>
+      <c r="AI32" s="8" t="n"/>
+      <c r="AJ32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -4452,13 +4800,17 @@
       <c r="AD33" s="8" t="n"/>
       <c r="AE33" s="8" t="n"/>
       <c r="AF33" s="8" t="n"/>
+      <c r="AG33" s="8" t="n"/>
+      <c r="AH33" s="8" t="n"/>
+      <c r="AI33" s="8" t="n"/>
+      <c r="AJ33" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A1:AJ1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30 AB31 AB32 AB33 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30 AB31 AB32 AB33 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33 AE5 AE6 AE7 AE8 AE9 AE10 AE11 AE12 AE13 AE14 AE15 AE16 AE17 AE18 AE19 AE20 AE21 AE22 AE23 AE24 AE25 AE26 AE27 AE28 AE29 AE30 AE31 AE32 AE33 AF5 AF6 AF7 AF8 AF9 AF10 AF11 AF12 AF13 AF14 AF15 AF16 AF17 AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25 AF26 AF27 AF28 AF29 AF30 AF31 AF32 AF33 AG5 AG6 AG7 AG8 AG9 AG10 AG11 AG12 AG13 AG14 AG15 AG16 AG17 AG18 AG19 AG20 AG21 AG22 AG23 AG24 AG25 AG26 AG27 AG28 AG29 AG30 AG31 AG32 AG33 AH5 AH6 AH7 AH8 AH9 AH10 AH11 AH12 AH13 AH14 AH15 AH16 AH17 AH18 AH19 AH20 AH21 AH22 AH23 AH24 AH25 AH26 AH27 AH28 AH29 AH30 AH31 AH32 AH33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -4472,7 +4824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4538,12 +4890,12 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>FLOOD_EVENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
+          <t>No. of Flood events_ 1974-2004_25%</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -4557,43 +4909,35 @@
       <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>FLOOD_HAZARD_INDEX</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Flood Hazard Index</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_1974_TO_2023</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>No. of lightning incidents  - 1974 to 2023</t>
+          <t>No. of Flood events_ 2005-2023_75%</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -4607,35 +4951,43 @@
       <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Strong wind events - 1978 to 2023</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>FLOOD_HAZARD_INDEX</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Flood Hazard Index</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="11" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>VERY_WET_DAYS</t>
+          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
+          <t>No. of lightning incidents  - 1974 to 2023</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -4651,17 +5003,17 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>ANNUAL_EGG_PRODUCTION</t>
+          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Egg Production (Annual)</t>
+          <t>Strong wind events - 1978 to 2023</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -4672,17 +5024,17 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY</t>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>No. of Backyard hatcheries -DOC production / weekly</t>
+          <t>3 day cumulative rain fall</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -4693,17 +5045,17 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>BACKYARD_POULTRY_FARMS</t>
+          <t>VERY_WET_DAYS</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>No. of Backyard Poultry Farms</t>
+          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
@@ -4714,17 +5066,17 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>BROILER_FARMS</t>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>No. of Broiler Farms</t>
+          <t>Very wet days (95th percentile)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D12" s="11" t="n"/>
@@ -4733,43 +5085,35 @@
       <c r="G12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>DAILY_EGG_PRODUCTION</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Daily Egg Production</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>ANNUAL_EGG_PRODUCTION</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Egg Production (Annual)</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>EGG_COLLECTORS</t>
+          <t>BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>No. of egg collectors</t>
+          <t>No. of Backyard hatcheries -DOC production / weekly</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -4785,12 +5129,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>EGG_LAYING_HENS</t>
+          <t>BACKYARD_POULTRY_FARMS</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>No. of Egg Laying Hens</t>
+          <t>No. of Backyard Poultry Farms</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -4806,12 +5150,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>FARM_SHOP</t>
+          <t>BROILER_FARMS</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>No. of farm shop</t>
+          <t>No. of Broiler Farms</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -4825,35 +5169,43 @@
       <c r="G16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>LAYER_FARMS</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>No. of Layer Farms</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>DAILY_EGG_PRODUCTION</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Daily Egg Production</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="11" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>LIVE_BIRD_COLLECTORS</t>
+          <t>EGG_COLLECTORS</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>No.of live bird collectors</t>
+          <t>No. of egg collectors</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -4869,12 +5221,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>MEAT_PROCESSING_PLANTS</t>
+          <t>EGG_LAYING_HENS</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>No. of meat processing plants</t>
+          <t>No. of Egg Laying Hens</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -4890,12 +5242,12 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>MONTHLY_EGG_PRODUCTION</t>
+          <t>FARM_SHOP</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Monthly Egg Production</t>
+          <t>No. of farm shop</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -4909,43 +5261,35 @@
       <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>% Poultry Farmers from total livestock farmers</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>LAYER_FARMS</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>No. of Layer Farms</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PCT_POULTRY_RAISING_FAMERS</t>
+          <t>LIVE_BIRD_COLLECTORS</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>% of Poultry raising famers</t>
+          <t>No.of live bird collectors</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -4959,43 +5303,35 @@
       <c r="G22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>POULTRY_FARMERS</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t># Poultry Farmers</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>MEAT_PROCESSING_PLANTS</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>No. of meat processing plants</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G23" s="13" t="inlineStr"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>POULTRY_FEED_MANUFACTURES_COMMERCIAL</t>
+          <t>MONTHLY_EGG_PRODUCTION</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>No. of poultry feed manufactures(commercial)</t>
+          <t>Monthly Egg Production</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -5009,85 +5345,93 @@
       <c r="G24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>POULTRY_FEED_SELF_MIXED_MIXERS</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>No. of poultry feed (self mixed) mixers</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>% Poultry Farmers from total livestock farmers</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="11" t="inlineStr"/>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>POULTRY_POPULATION</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Poultry Population</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>PCT_POULTRY_RAISING_FAMERS</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>% of Poultry raising famers</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>POULTRY_FARMERS</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t># Poultry Farmers</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E27" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>SLAUGHTER_HOUSES_MUNICIPAL</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>No. of slaughter houses ( municipal )</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="11" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS</t>
+          <t>POULTRY_FEED_MANUFACTURES_COMMERCIAL</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>No. of small scale poultry processing establishments ( manual processors)</t>
+          <t>No. of poultry feed manufactures(commercial)</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -5100,25 +5444,117 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="11" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>POULTRY_FEED_SELF_MIXED_MIXERS</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>No. of poultry feed (self mixed) mixers</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="11" t="inlineStr"/>
+    </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>POULTRY_POPULATION</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Poultry Population</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>SLAUGHTER_HOUSES_MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>No. of slaughter houses ( municipal )</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>No. of small scale poultry processing establishments ( manual processors)</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>SUM - hazard (must equal 100)</t>
         </is>
       </c>
-      <c r="F30" s="15">
-        <f>F4+F5+F6+F7+F8</f>
+      <c r="F34" s="15">
+        <f>F4+F5+F6+F7+F8+F9+F10+F11+F12</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>SUM - exposure (must equal 100)</t>
         </is>
       </c>
-      <c r="F31" s="15">
-        <f>F9+F10+F11+F12+F13+F14+F15+F16+F17+F18+F19+F20+F21+F22+F23+F24+F25+F26+F27+F28</f>
+      <c r="F35" s="15">
+        <f>F13+F14+F15+F16+F17+F18+F19+F20+F21+F22+F23+F24+F25+F26+F27+F28+F29+F30+F31+F32</f>
         <v/>
       </c>
     </row>
@@ -5127,7 +5563,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -5142,7 +5578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5163,7 +5599,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: POULTRY_FLOOD_NCE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: POULTRY_FLOOD_NCE_V1   |   generated 2026-09-14 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
@@ -5189,9 +5625,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>3. The yellow cells are where data belongs. Division codes, names, district and the period columns are pre-filled - change one only to correct a genuine error. Nothing in this file is protected, so please treat that as the instruction it is; the importer checks those columns and will refuse what it cannot match.</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5641,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
+          <t>5. Do not add, remove, rename or reorder columns or tabs. Excel will now let you - the sheet is not protected - but the importer will not: the hidden _META tab states this file's column contract and a file whose structure has changed is refused, naming what changed. Nothing loads partially, so a rejected file loads nothing at all.</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5715,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>FLOOD_EVENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
+          <t>No. of Flood events_ 1974-2004_25%</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -5296,19 +5732,19 @@
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>fixed window - same value on both period tabs</t>
+          <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>FLOOD_HAZARD_INDEX</t>
+          <t>FLOOD_EVENTS_1974_TO_2023</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Flood Hazard Index</t>
+          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -5316,14 +5752,8 @@
           <t>hazard</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>100</v>
-      </c>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
           <t>fixed window - same value on both period tabs</t>
@@ -5333,12 +5763,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>No. of lightning incidents  - 1974 to 2023</t>
+          <t>No. of Flood events_ 2005-2023_75%</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -5350,19 +5780,19 @@
       <c r="E20" s="13" t="n"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>fixed window - same value on both period tabs</t>
+          <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
+          <t>FLOOD_HAZARD_INDEX</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Strong wind events - 1978 to 2023</t>
+          <t>Flood Hazard Index</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -5370,8 +5800,14 @@
           <t>hazard</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
           <t>fixed window - same value on both period tabs</t>
@@ -5381,12 +5817,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>VERY_WET_DAYS</t>
+          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
+          <t>No. of lightning incidents  - 1974 to 2023</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -5398,48 +5834,48 @@
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>enter a TYPICAL YEAR (not a total)</t>
+          <t>fixed window - same value on both period tabs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>ANNUAL_EGG_PRODUCTION</t>
+          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Egg Production (Annual)</t>
+          <t>Strong wind events - 1978 to 2023</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
       <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>enter a TYPICAL YEAR (not a total)</t>
+          <t>fixed window - same value on both period tabs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY</t>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>No. of Backyard hatcheries -DOC production / weekly</t>
+          <t>3 day cumulative rain fall</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
@@ -5453,17 +5889,17 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>BACKYARD_POULTRY_FARMS</t>
+          <t>VERY_WET_DAYS</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>No. of Backyard Poultry Farms</t>
+          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
@@ -5477,17 +5913,17 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>BROILER_FARMS</t>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>No. of Broiler Farms</t>
+          <t>Very wet days (95th percentile)</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
@@ -5501,12 +5937,12 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>DAILY_EGG_PRODUCTION</t>
+          <t>ANNUAL_EGG_PRODUCTION</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Daily Egg Production</t>
+          <t>Egg Production (Annual)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -5514,14 +5950,8 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>25</v>
-      </c>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -5531,12 +5961,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>EGG_COLLECTORS</t>
+          <t>BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>No. of egg collectors</t>
+          <t>No. of Backyard hatcheries -DOC production / weekly</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -5555,12 +5985,12 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>EGG_LAYING_HENS</t>
+          <t>BACKYARD_POULTRY_FARMS</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>No. of Egg Laying Hens</t>
+          <t>No. of Backyard Poultry Farms</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -5579,12 +6009,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>FARM_SHOP</t>
+          <t>BROILER_FARMS</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>No. of farm shop</t>
+          <t>No. of Broiler Farms</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -5603,12 +6033,12 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>LAYER_FARMS</t>
+          <t>DAILY_EGG_PRODUCTION</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>No. of Layer Farms</t>
+          <t>Daily Egg Production</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -5616,8 +6046,14 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>25</v>
+      </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -5627,12 +6063,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>LIVE_BIRD_COLLECTORS</t>
+          <t>EGG_COLLECTORS</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>No.of live bird collectors</t>
+          <t>No. of egg collectors</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -5651,12 +6087,12 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>MEAT_PROCESSING_PLANTS</t>
+          <t>EGG_LAYING_HENS</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>No. of meat processing plants</t>
+          <t>No. of Egg Laying Hens</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -5675,12 +6111,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>MONTHLY_EGG_PRODUCTION</t>
+          <t>FARM_SHOP</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Monthly Egg Production</t>
+          <t>No. of farm shop</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -5699,12 +6135,12 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS</t>
+          <t>LAYER_FARMS</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>% Poultry Farmers from total livestock farmers</t>
+          <t>No. of Layer Farms</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -5712,14 +6148,8 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="n">
-        <v>25</v>
-      </c>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -5729,12 +6159,12 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PCT_POULTRY_RAISING_FAMERS</t>
+          <t>LIVE_BIRD_COLLECTORS</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>% of Poultry raising famers</t>
+          <t>No.of live bird collectors</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -5753,12 +6183,12 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>POULTRY_FARMERS</t>
+          <t>MEAT_PROCESSING_PLANTS</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t># Poultry Farmers</t>
+          <t>No. of meat processing plants</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -5766,14 +6196,8 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>25</v>
-      </c>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
       <c r="F37" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -5783,12 +6207,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>POULTRY_FEED_MANUFACTURES_COMMERCIAL</t>
+          <t>MONTHLY_EGG_PRODUCTION</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>No. of poultry feed manufactures(commercial)</t>
+          <t>Monthly Egg Production</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -5807,12 +6231,12 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>POULTRY_FEED_SELF_MIXED_MIXERS</t>
+          <t>PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>No. of poultry feed (self mixed) mixers</t>
+          <t>% Poultry Farmers from total livestock farmers</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -5820,8 +6244,14 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>25</v>
+      </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -5831,12 +6261,12 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>POULTRY_POPULATION</t>
+          <t>PCT_POULTRY_RAISING_FAMERS</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Poultry Population</t>
+          <t>% of Poultry raising famers</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
@@ -5844,14 +6274,8 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>25</v>
-      </c>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
       <c r="F40" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -5861,12 +6285,12 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>SLAUGHTER_HOUSES_MUNICIPAL</t>
+          <t>POULTRY_FARMERS</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>No. of slaughter houses ( municipal )</t>
+          <t># Poultry Farmers</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -5874,8 +6298,14 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>25</v>
+      </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -5885,12 +6315,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS</t>
+          <t>POULTRY_FEED_MANUFACTURES_COMMERCIAL</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>No. of small scale poultry processing establishments ( manual processors)</t>
+          <t>No. of poultry feed manufactures(commercial)</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -5901,6 +6331,108 @@
       <c r="D42" s="13" t="n"/>
       <c r="E42" s="13" t="n"/>
       <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>POULTRY_FEED_SELF_MIXED_MIXERS</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>No. of poultry feed (self mixed) mixers</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>POULTRY_POPULATION</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Poultry Population</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>SLAUGHTER_HOUSES_MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>No. of slaughter houses ( municipal )</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>No. of small scale poultry processing establishments ( manual processors)</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
@@ -6010,7 +6542,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>unlocked-review</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6554,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>0 add, 0 retire</t>
+          <t>4 add, 0 retire</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6566,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6601,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -6092,7 +6624,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|ANNUAL_EGG_PRODUCTION=average|BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY=average|BACKYARD_POULTRY_FARMS=average|BROILER_FARMS=average|DAILY_EGG_PRODUCTION=average|EGG_COLLECTORS=average|EGG_LAYING_HENS=average|FARM_SHOP=average|LAYER_FARMS=average|LIVE_BIRD_COLLECTORS=average|MEAT_PROCESSING_PLANTS=average|MONTHLY_EGG_PRODUCTION=average|PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS=average|PCT_POULTRY_RAISING_FAMERS=average|POULTRY_FARMERS=average|POULTRY_FEED_MANUFACTURES_COMMERCIAL=average|POULTRY_FEED_SELF_MIXED_MIXERS=average|POULTRY_POPULATION=average|SLAUGHTER_HOUSES_MUNICIPAL=average|SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS=average</t>
+          <t>FLOOD_EVENTS_1974_TO_2004=average|FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_EVENTS_2005_TO_2023=average|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|THREE_DAY_CUMULATIVE_RAINFALL=average|VERY_WET_DAYS=average|VERY_WET_DAYS_95TH_PERCENTILE=average|ANNUAL_EGG_PRODUCTION=average|BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY=average|BACKYARD_POULTRY_FARMS=average|BROILER_FARMS=average|DAILY_EGG_PRODUCTION=average|EGG_COLLECTORS=average|EGG_LAYING_HENS=average|FARM_SHOP=average|LAYER_FARMS=average|LIVE_BIRD_COLLECTORS=average|MEAT_PROCESSING_PLANTS=average|MONTHLY_EGG_PRODUCTION=average|PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS=average|PCT_POULTRY_RAISING_FAMERS=average|POULTRY_FARMERS=average|POULTRY_FEED_MANUFACTURES_COMMERCIAL=average|POULTRY_FEED_SELF_MIXED_MIXERS=average|POULTRY_POPULATION=average|SLAUGHTER_HOUSES_MUNICIPAL=average|SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS=average</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6636,7 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|VERY_WET_DAYS|ANNUAL_EGG_PRODUCTION|BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY|BACKYARD_POULTRY_FARMS|BROILER_FARMS|DAILY_EGG_PRODUCTION|EGG_COLLECTORS|EGG_LAYING_HENS|FARM_SHOP|LAYER_FARMS|LIVE_BIRD_COLLECTORS|MEAT_PROCESSING_PLANTS|MONTHLY_EGG_PRODUCTION|PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS|PCT_POULTRY_RAISING_FAMERS|POULTRY_FARMERS|POULTRY_FEED_MANUFACTURES_COMMERCIAL|POULTRY_FEED_SELF_MIXED_MIXERS|POULTRY_POPULATION|SLAUGHTER_HOUSES_MUNICIPAL|SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS|DATA_SOURCE|NOTES</t>
+          <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2004|FLOOD_EVENTS_1974_TO_2023|FLOOD_EVENTS_2005_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|THREE_DAY_CUMULATIVE_RAINFALL|VERY_WET_DAYS|VERY_WET_DAYS_95TH_PERCENTILE|ANNUAL_EGG_PRODUCTION|BACKYARD_HATCHERIES_DOC_PRODUCTION_WEEKLY|BACKYARD_POULTRY_FARMS|BROILER_FARMS|DAILY_EGG_PRODUCTION|EGG_COLLECTORS|EGG_LAYING_HENS|FARM_SHOP|LAYER_FARMS|LIVE_BIRD_COLLECTORS|MEAT_PROCESSING_PLANTS|MONTHLY_EGG_PRODUCTION|PCT_POULTRY_FARMERS_LIVESTOCK_OPERATORS|PCT_POULTRY_RAISING_FAMERS|POULTRY_FARMERS|POULTRY_FEED_MANUFACTURES_COMMERCIAL|POULTRY_FEED_SELF_MIXED_MIXERS|POULTRY_POPULATION|SLAUGHTER_HOUSES_MUNICIPAL|SMALL_SCALE_POULTRY_PROCESSING_ESTABLISHMENTS|DATA_SOURCE|NOTES</t>
         </is>
       </c>
     </row>
